--- a/cet4/result/24_重生商女_豪门弃女归来/24_重生商女_豪门弃女归来_学习版.xlsx
+++ b/cet4/result/24_重生商女_豪门弃女归来/24_重生商女_豪门弃女归来_学习版.xlsx
@@ -397,605 +397,451 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D42"/>
+  <dimension ref="A1:D31"/>
   <cols>
-    <col min="1" max="1" width="8.83203125" customWidth="1"/>
+    <col min="1" max="1" width="15.83203125" customWidth="1"/>
     <col min="2" max="2" width="20.83203125" customWidth="1"/>
-    <col min="3" max="3" width="30.83203125" customWidth="1"/>
-    <col min="4" max="4" width="40.83203125" customWidth="1"/>
+    <col min="3" max="3" width="15.83203125" customWidth="1"/>
+    <col min="4" max="4" width="30.83203125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
-        <v>序号</v>
+        <v>词汇</v>
       </c>
       <c r="B1" t="str">
-        <v>单词</v>
+        <v>音标</v>
       </c>
       <c r="C1" t="str">
-        <v>中文释义</v>
+        <v>词性</v>
       </c>
       <c r="D1" t="str">
-        <v>完整形式</v>
+        <v>中文</v>
       </c>
     </row>
     <row r="2">
-      <c r="A2">
-        <v>1</v>
+      <c r="A2" t="str">
+        <v>table</v>
       </c>
       <c r="B2" t="str">
-        <v>table</v>
+        <v>/ˈteɪbl/</v>
       </c>
       <c r="C2" t="str">
+        <v>n./vt./adj.</v>
+      </c>
+      <c r="D2" t="str">
         <v>桌子</v>
       </c>
-      <c r="D2" t="str">
-        <v>table(桌子)📢</v>
-      </c>
     </row>
     <row r="3">
-      <c r="A3">
-        <v>2</v>
+      <c r="A3" t="str">
+        <v>anger</v>
       </c>
       <c r="B3" t="str">
-        <v>anger</v>
+        <v>/ˈæŋɡər/</v>
       </c>
       <c r="C3" t="str">
+        <v>n./vt./vi.</v>
+      </c>
+      <c r="D3" t="str">
         <v>愤怒</v>
       </c>
-      <c r="D3" t="str">
-        <v>anger(愤怒)📢</v>
-      </c>
     </row>
     <row r="4">
-      <c r="A4">
-        <v>3</v>
+      <c r="A4" t="str">
+        <v>division</v>
       </c>
       <c r="B4" t="str">
-        <v>division</v>
+        <v>/dɪˈvɪʒn/</v>
       </c>
       <c r="C4" t="str">
+        <v>n.</v>
+      </c>
+      <c r="D4" t="str">
         <v>部门</v>
       </c>
-      <c r="D4" t="str">
-        <v>division(部门)📢</v>
-      </c>
     </row>
     <row r="5">
-      <c r="A5">
-        <v>4</v>
+      <c r="A5" t="str">
+        <v>America</v>
       </c>
       <c r="B5" t="str">
-        <v>America</v>
+        <v>/əˈmerɪkə/</v>
       </c>
       <c r="C5" t="str">
+        <v>n.</v>
+      </c>
+      <c r="D5" t="str">
         <v>美国</v>
       </c>
-      <c r="D5" t="str">
-        <v>America(美国)📢</v>
-      </c>
     </row>
     <row r="6">
-      <c r="A6">
-        <v>5</v>
+      <c r="A6" t="str">
+        <v>display</v>
       </c>
       <c r="B6" t="str">
-        <v>display</v>
+        <v>/dɪˈspleɪ/</v>
       </c>
       <c r="C6" t="str">
+        <v>n./vt./vi./adj.</v>
+      </c>
+      <c r="D6" t="str">
         <v>展示</v>
       </c>
-      <c r="D6" t="str">
-        <v>display(展示)📢</v>
-      </c>
     </row>
     <row r="7">
-      <c r="A7">
-        <v>6</v>
+      <c r="A7" t="str">
+        <v>central</v>
       </c>
       <c r="B7" t="str">
-        <v>central</v>
+        <v>/ˈsentrəl/</v>
       </c>
       <c r="C7" t="str">
+        <v>n./adj.</v>
+      </c>
+      <c r="D7" t="str">
         <v>中心的</v>
       </c>
-      <c r="D7" t="str">
-        <v>central(中心的)📢</v>
-      </c>
     </row>
     <row r="8">
-      <c r="A8">
-        <v>7</v>
+      <c r="A8" t="str">
+        <v>approval</v>
       </c>
       <c r="B8" t="str">
-        <v>approval</v>
+        <v>/əˈpruːvl/</v>
       </c>
       <c r="C8" t="str">
+        <v>n.</v>
+      </c>
+      <c r="D8" t="str">
         <v>批准</v>
       </c>
-      <c r="D8" t="str">
-        <v>approval(批准)📢</v>
-      </c>
     </row>
     <row r="9">
-      <c r="A9">
-        <v>8</v>
+      <c r="A9" t="str">
+        <v>defeat</v>
       </c>
       <c r="B9" t="str">
-        <v>defeat</v>
+        <v>/dɪˈfiːt/</v>
       </c>
       <c r="C9" t="str">
+        <v>n./v.</v>
+      </c>
+      <c r="D9" t="str">
         <v>击败</v>
       </c>
-      <c r="D9" t="str">
-        <v>defeat(击败)📢</v>
-      </c>
     </row>
     <row r="10">
-      <c r="A10">
-        <v>9</v>
+      <c r="A10" t="str">
+        <v>goal</v>
       </c>
       <c r="B10" t="str">
-        <v>table</v>
+        <v>/ɡoʊl/</v>
       </c>
       <c r="C10" t="str">
-        <v>桌子</v>
+        <v>n./vi.</v>
       </c>
       <c r="D10" t="str">
-        <v>table(桌子)📢</v>
+        <v>目标</v>
       </c>
     </row>
     <row r="11">
-      <c r="A11">
-        <v>10</v>
+      <c r="A11" t="str">
+        <v>aero</v>
       </c>
       <c r="B11" t="str">
-        <v>goal</v>
+        <v>/ˈeroʊ/</v>
       </c>
       <c r="C11" t="str">
-        <v>目标</v>
+        <v>adj.</v>
       </c>
       <c r="D11" t="str">
-        <v>goal(目标)📢</v>
+        <v>航空</v>
       </c>
     </row>
     <row r="12">
-      <c r="A12">
-        <v>11</v>
+      <c r="A12" t="str">
+        <v>abundant</v>
       </c>
       <c r="B12" t="str">
-        <v>aero</v>
+        <v>/əˈbʌndənt/</v>
       </c>
       <c r="C12" t="str">
-        <v>航空</v>
+        <v>adj.</v>
       </c>
       <c r="D12" t="str">
-        <v>aero(航空)📢</v>
+        <v>丰富的</v>
       </c>
     </row>
     <row r="13">
-      <c r="A13">
-        <v>12</v>
+      <c r="A13" t="str">
+        <v>suspect</v>
       </c>
       <c r="B13" t="str">
-        <v>abundant</v>
+        <v>/səˈspekt/</v>
       </c>
       <c r="C13" t="str">
-        <v>丰富的</v>
+        <v>n./v./adj.</v>
       </c>
       <c r="D13" t="str">
-        <v>abundant(丰富的)📢</v>
+        <v>怀疑</v>
       </c>
     </row>
     <row r="14">
-      <c r="A14">
-        <v>13</v>
+      <c r="A14" t="str">
+        <v>garage</v>
       </c>
       <c r="B14" t="str">
-        <v>suspect</v>
+        <v>/ˈɡærɑːʒ/</v>
       </c>
       <c r="C14" t="str">
-        <v>怀疑</v>
+        <v>n./vt.</v>
       </c>
       <c r="D14" t="str">
-        <v>suspect(怀疑)📢</v>
+        <v>车库</v>
       </c>
     </row>
     <row r="15">
-      <c r="A15">
-        <v>14</v>
+      <c r="A15" t="str">
+        <v>offend</v>
       </c>
       <c r="B15" t="str">
-        <v>table</v>
+        <v>/əˈfend/</v>
       </c>
       <c r="C15" t="str">
-        <v>桌子</v>
+        <v>vt./vi.</v>
       </c>
       <c r="D15" t="str">
-        <v>table(桌子)📢</v>
+        <v>冒犯</v>
       </c>
     </row>
     <row r="16">
-      <c r="A16">
-        <v>15</v>
+      <c r="A16" t="str">
+        <v>purchase</v>
       </c>
       <c r="B16" t="str">
-        <v>garage</v>
+        <v>/ˈpɜːrtʃəs/</v>
       </c>
       <c r="C16" t="str">
-        <v>车库</v>
+        <v>n./v.</v>
       </c>
       <c r="D16" t="str">
-        <v>garage(车库)📢</v>
+        <v>购买</v>
       </c>
     </row>
     <row r="17">
-      <c r="A17">
-        <v>16</v>
+      <c r="A17" t="str">
+        <v>accumulate</v>
       </c>
       <c r="B17" t="str">
-        <v>offend</v>
+        <v>/əˈkjuːmjəleɪt/</v>
       </c>
       <c r="C17" t="str">
-        <v>冒犯</v>
+        <v>vt./vi.</v>
       </c>
       <c r="D17" t="str">
-        <v>offend(冒犯)📢</v>
+        <v>积累</v>
       </c>
     </row>
     <row r="18">
-      <c r="A18">
-        <v>17</v>
+      <c r="A18" t="str">
+        <v>apple</v>
       </c>
       <c r="B18" t="str">
-        <v>purchase</v>
+        <v>/ˈæpl/</v>
       </c>
       <c r="C18" t="str">
-        <v>购买</v>
+        <v>n.</v>
       </c>
       <c r="D18" t="str">
-        <v>purchase(购买)📢</v>
+        <v>苹果</v>
       </c>
     </row>
     <row r="19">
-      <c r="A19">
-        <v>18</v>
+      <c r="A19" t="str">
+        <v>down</v>
       </c>
       <c r="B19" t="str">
-        <v>division</v>
+        <v>/daʊn/</v>
       </c>
       <c r="C19" t="str">
-        <v>部门</v>
+        <v>n./v./adj./adv./prep.</v>
       </c>
       <c r="D19" t="str">
-        <v>division(部门)📢</v>
+        <v>向下</v>
       </c>
     </row>
     <row r="20">
-      <c r="A20">
-        <v>19</v>
+      <c r="A20" t="str">
+        <v>athlete</v>
       </c>
       <c r="B20" t="str">
-        <v>accumulate</v>
+        <v>/ˈæθliːt/</v>
       </c>
       <c r="C20" t="str">
-        <v>积累</v>
+        <v>n.</v>
       </c>
       <c r="D20" t="str">
-        <v>accumulate(积累)📢</v>
+        <v>运动员</v>
       </c>
     </row>
     <row r="21">
-      <c r="A21">
-        <v>20</v>
+      <c r="A21" t="str">
+        <v>profession</v>
       </c>
       <c r="B21" t="str">
-        <v>apple</v>
+        <v>/prəˈfeʃn/</v>
       </c>
       <c r="C21" t="str">
-        <v>苹果</v>
+        <v>n.</v>
       </c>
       <c r="D21" t="str">
-        <v>apple(苹果)📢</v>
+        <v>职业</v>
       </c>
     </row>
     <row r="22">
-      <c r="A22">
-        <v>21</v>
+      <c r="A22" t="str">
+        <v>evidence</v>
       </c>
       <c r="B22" t="str">
-        <v>down</v>
+        <v>/ˈevɪdəns/</v>
       </c>
       <c r="C22" t="str">
-        <v>向下</v>
+        <v>n./vt.</v>
       </c>
       <c r="D22" t="str">
-        <v>down(向下)📢</v>
+        <v>证据</v>
       </c>
     </row>
     <row r="23">
-      <c r="A23">
-        <v>22</v>
+      <c r="A23" t="str">
+        <v>exhibition</v>
       </c>
       <c r="B23" t="str">
-        <v>athlete</v>
+        <v>/ˌeksɪˈbɪʃn/</v>
       </c>
       <c r="C23" t="str">
-        <v>运动员</v>
+        <v>n.</v>
       </c>
       <c r="D23" t="str">
-        <v>athlete(运动员)📢</v>
+        <v>展览</v>
       </c>
     </row>
     <row r="24">
-      <c r="A24">
-        <v>23</v>
+      <c r="A24" t="str">
+        <v>stranger</v>
       </c>
       <c r="B24" t="str">
-        <v>America</v>
+        <v>/ˈstreɪndʒər/</v>
       </c>
       <c r="C24" t="str">
-        <v>美国</v>
+        <v>n.</v>
       </c>
       <c r="D24" t="str">
-        <v>America(美国)📢</v>
+        <v>陌生人</v>
       </c>
     </row>
     <row r="25">
-      <c r="A25">
-        <v>24</v>
+      <c r="A25" t="str">
+        <v>conference</v>
       </c>
       <c r="B25" t="str">
-        <v>profession</v>
+        <v>/ˈkɑːnfərəns/</v>
       </c>
       <c r="C25" t="str">
-        <v>职业</v>
+        <v>n./vi.</v>
       </c>
       <c r="D25" t="str">
-        <v>profession(职业)📢</v>
+        <v>会议</v>
       </c>
     </row>
     <row r="26">
-      <c r="A26">
-        <v>25</v>
+      <c r="A26" t="str">
+        <v>largely</v>
       </c>
       <c r="B26" t="str">
-        <v>evidence</v>
+        <v>/ˈlɑːrdʒli/</v>
       </c>
       <c r="C26" t="str">
-        <v>证据</v>
+        <v>v./adv.</v>
       </c>
       <c r="D26" t="str">
-        <v>evidence(证据)📢</v>
+        <v>主要地</v>
       </c>
     </row>
     <row r="27">
-      <c r="A27">
-        <v>26</v>
+      <c r="A27" t="str">
+        <v>honour</v>
       </c>
       <c r="B27" t="str">
-        <v>exhibition</v>
+        <v>/ˈɑːnər/</v>
       </c>
       <c r="C27" t="str">
-        <v>展览</v>
+        <v>n./vt.</v>
       </c>
       <c r="D27" t="str">
-        <v>exhibition(展览)📢</v>
+        <v>荣誉</v>
       </c>
     </row>
     <row r="28">
-      <c r="A28">
-        <v>27</v>
+      <c r="A28" t="str">
+        <v>wealthy</v>
       </c>
       <c r="B28" t="str">
-        <v>stranger</v>
+        <v>/ˈwelθi/</v>
       </c>
       <c r="C28" t="str">
-        <v>陌生人</v>
+        <v>n./adj.</v>
       </c>
       <c r="D28" t="str">
-        <v>stranger(陌生人)📢</v>
+        <v>富有的</v>
       </c>
     </row>
     <row r="29">
-      <c r="A29">
-        <v>28</v>
+      <c r="A29" t="str">
+        <v>audience</v>
       </c>
       <c r="B29" t="str">
-        <v>evidence</v>
+        <v>/ˈɔːdiəns/</v>
       </c>
       <c r="C29" t="str">
-        <v>证据</v>
+        <v>n.</v>
       </c>
       <c r="D29" t="str">
-        <v>evidence(证据)📢</v>
+        <v>观众</v>
       </c>
     </row>
     <row r="30">
-      <c r="A30">
-        <v>29</v>
+      <c r="A30" t="str">
+        <v>hopeful</v>
       </c>
       <c r="B30" t="str">
-        <v>conference</v>
+        <v>/ˈhoʊpfl/</v>
       </c>
       <c r="C30" t="str">
-        <v>会议</v>
+        <v>n./adj.</v>
       </c>
       <c r="D30" t="str">
-        <v>conference(会议)📢</v>
+        <v>有希望的</v>
       </c>
     </row>
     <row r="31">
-      <c r="A31">
-        <v>30</v>
+      <c r="A31" t="str">
+        <v>lead</v>
       </c>
       <c r="B31" t="str">
-        <v>conference</v>
+        <v>/liːd; led/</v>
       </c>
       <c r="C31" t="str">
-        <v>会议</v>
+        <v>n./vt./vi.</v>
       </c>
       <c r="D31" t="str">
-        <v>conference(会议)📢</v>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32">
-        <v>31</v>
-      </c>
-      <c r="B32" t="str">
-        <v>table</v>
-      </c>
-      <c r="C32" t="str">
-        <v>桌子</v>
-      </c>
-      <c r="D32" t="str">
-        <v>table(桌子)📢</v>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33">
-        <v>32</v>
-      </c>
-      <c r="B33" t="str">
-        <v>largely</v>
-      </c>
-      <c r="C33" t="str">
-        <v>主要地</v>
-      </c>
-      <c r="D33" t="str">
-        <v>largely(主要地)📢</v>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34">
-        <v>33</v>
-      </c>
-      <c r="B34" t="str">
-        <v>evidence</v>
-      </c>
-      <c r="C34" t="str">
-        <v>证据</v>
-      </c>
-      <c r="D34" t="str">
-        <v>evidence(证据)📢</v>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35">
-        <v>34</v>
-      </c>
-      <c r="B35" t="str">
-        <v>honour</v>
-      </c>
-      <c r="C35" t="str">
-        <v>荣誉</v>
-      </c>
-      <c r="D35" t="str">
-        <v>honour(荣誉)📢</v>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36">
-        <v>35</v>
-      </c>
-      <c r="B36" t="str">
-        <v>division</v>
-      </c>
-      <c r="C36" t="str">
-        <v>部门</v>
-      </c>
-      <c r="D36" t="str">
-        <v>division(部门)📢</v>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37">
-        <v>36</v>
-      </c>
-      <c r="B37" t="str">
-        <v>wealthy</v>
-      </c>
-      <c r="C37" t="str">
-        <v>富有的</v>
-      </c>
-      <c r="D37" t="str">
-        <v>wealthy(富有的)📢</v>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38">
-        <v>37</v>
-      </c>
-      <c r="B38" t="str">
-        <v>defeat</v>
-      </c>
-      <c r="C38" t="str">
-        <v>击败</v>
-      </c>
-      <c r="D38" t="str">
-        <v>defeat(击败)📢</v>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39">
-        <v>38</v>
-      </c>
-      <c r="B39" t="str">
-        <v>audience</v>
-      </c>
-      <c r="C39" t="str">
-        <v>观众</v>
-      </c>
-      <c r="D39" t="str">
-        <v>audience(观众)📢</v>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40">
-        <v>39</v>
-      </c>
-      <c r="B40" t="str">
-        <v>hopeful</v>
-      </c>
-      <c r="C40" t="str">
-        <v>有希望的</v>
-      </c>
-      <c r="D40" t="str">
-        <v>hopeful(有希望的)📢</v>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41">
-        <v>40</v>
-      </c>
-      <c r="B41" t="str">
-        <v>aero</v>
-      </c>
-      <c r="C41" t="str">
-        <v>航空</v>
-      </c>
-      <c r="D41" t="str">
-        <v>aero(航空)📢</v>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42">
-        <v>41</v>
-      </c>
-      <c r="B42" t="str">
-        <v>lead</v>
-      </c>
-      <c r="C42" t="str">
         <v>领导</v>
-      </c>
-      <c r="D42" t="str">
-        <v>lead(领导)📢</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:D42"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:D31"/>
   </ignoredErrors>
 </worksheet>
 </file>